--- a/src/data/COREP_files/G_EU_C_C0700.xlsx
+++ b/src/data/COREP_files/G_EU_C_C0700.xlsx
@@ -2755,19 +2755,25 @@
       <c r="K16" s="48" t="n"/>
       <c r="L16" s="48" t="n"/>
       <c r="M16" s="48" t="n"/>
-      <c r="N16" s="48" t="n"/>
+      <c r="N16" s="48" t="n">
+        <v>88</v>
+      </c>
       <c r="O16" s="47" t="n"/>
       <c r="P16" s="48" t="n"/>
       <c r="Q16" s="47" t="n"/>
       <c r="R16" s="49" t="n"/>
       <c r="S16" s="49" t="n"/>
       <c r="T16" s="49" t="n"/>
-      <c r="U16" s="49" t="n"/>
+      <c r="U16" s="49" t="n">
+        <v>95</v>
+      </c>
       <c r="V16" s="49" t="n"/>
       <c r="W16" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="X16" s="51" t="n"/>
+      <c r="X16" s="51" t="n">
+        <v>89</v>
+      </c>
       <c r="Y16" s="52" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -2807,19 +2813,25 @@
       <c r="K17" s="58" t="n"/>
       <c r="L17" s="58" t="n"/>
       <c r="M17" s="58" t="n"/>
-      <c r="N17" s="58" t="n"/>
+      <c r="N17" s="58" t="n">
+        <v>89</v>
+      </c>
       <c r="O17" s="58" t="n"/>
       <c r="P17" s="58" t="n"/>
       <c r="Q17" s="58" t="n"/>
       <c r="R17" s="59" t="n"/>
       <c r="S17" s="59" t="n"/>
       <c r="T17" s="59" t="n"/>
-      <c r="U17" s="59" t="n"/>
+      <c r="U17" s="59" t="n">
+        <v>96</v>
+      </c>
       <c r="V17" s="59" t="n"/>
       <c r="W17" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="X17" s="60" t="n"/>
+      <c r="X17" s="60" t="n">
+        <v>90</v>
+      </c>
       <c r="Y17" s="61" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -2845,7 +2857,9 @@
           <t xml:space="preserve">of which: SME subject to SME-supporting factor </t>
         </is>
       </c>
-      <c r="D18" s="66" t="n"/>
+      <c r="D18" s="66" t="n">
+        <v>89</v>
+      </c>
       <c r="E18" s="57" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="67" t="n"/>
@@ -2855,19 +2869,25 @@
       <c r="K18" s="67" t="n"/>
       <c r="L18" s="67" t="n"/>
       <c r="M18" s="67" t="n"/>
-      <c r="N18" s="67" t="n"/>
+      <c r="N18" s="67" t="n">
+        <v>90</v>
+      </c>
       <c r="O18" s="67" t="n"/>
       <c r="P18" s="67" t="n"/>
       <c r="Q18" s="67" t="n"/>
       <c r="R18" s="68" t="n"/>
       <c r="S18" s="68" t="n"/>
       <c r="T18" s="68" t="n"/>
-      <c r="U18" s="68" t="n"/>
+      <c r="U18" s="68" t="n">
+        <v>97</v>
+      </c>
       <c r="V18" s="68" t="n"/>
       <c r="W18" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="X18" s="61" t="n"/>
+      <c r="X18" s="61" t="n">
+        <v>91</v>
+      </c>
       <c r="Y18" s="61" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -2931,7 +2951,9 @@
           <t>of which: Exposures under the permanent partial use of the standardised approach</t>
         </is>
       </c>
-      <c r="D20" s="70" t="n"/>
+      <c r="D20" s="70" t="n">
+        <v>91</v>
+      </c>
       <c r="E20" s="57" t="n"/>
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="58" t="n"/>
@@ -2941,19 +2963,25 @@
       <c r="K20" s="58" t="n"/>
       <c r="L20" s="58" t="n"/>
       <c r="M20" s="58" t="n"/>
-      <c r="N20" s="58" t="n"/>
+      <c r="N20" s="58" t="n">
+        <v>92</v>
+      </c>
       <c r="O20" s="58" t="n"/>
       <c r="P20" s="58" t="n"/>
       <c r="Q20" s="58" t="n"/>
       <c r="R20" s="59" t="n"/>
       <c r="S20" s="59" t="n"/>
       <c r="T20" s="59" t="n"/>
-      <c r="U20" s="59" t="n"/>
+      <c r="U20" s="59" t="n">
+        <v>2</v>
+      </c>
       <c r="V20" s="59" t="n"/>
       <c r="W20" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="X20" s="60" t="n"/>
+      <c r="X20" s="60" t="n">
+        <v>93</v>
+      </c>
       <c r="Y20" s="61" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -2979,7 +3007,9 @@
           <t>of which: Exposures under the standardised approach with prior supervisory permission to carry out a sequential IRB implementation</t>
         </is>
       </c>
-      <c r="D21" s="71" t="n"/>
+      <c r="D21" s="71" t="n">
+        <v>92</v>
+      </c>
       <c r="E21" s="72" t="n"/>
       <c r="F21" s="73" t="n"/>
       <c r="G21" s="73" t="n"/>
@@ -2989,19 +3019,25 @@
       <c r="K21" s="73" t="n"/>
       <c r="L21" s="73" t="n"/>
       <c r="M21" s="73" t="n"/>
-      <c r="N21" s="73" t="n"/>
+      <c r="N21" s="73" t="n">
+        <v>93</v>
+      </c>
       <c r="O21" s="73" t="n"/>
       <c r="P21" s="73" t="n"/>
       <c r="Q21" s="73" t="n"/>
       <c r="R21" s="74" t="n"/>
       <c r="S21" s="74" t="n"/>
       <c r="T21" s="74" t="n"/>
-      <c r="U21" s="74" t="n"/>
+      <c r="U21" s="74" t="n">
+        <v>3</v>
+      </c>
       <c r="V21" s="74" t="n"/>
       <c r="W21" s="75" t="n">
         <v>1</v>
       </c>
-      <c r="X21" s="75" t="n"/>
+      <c r="X21" s="75" t="n">
+        <v>94</v>
+      </c>
       <c r="Y21" s="76" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -3073,19 +3109,25 @@
       <c r="K23" s="83" t="n"/>
       <c r="L23" s="83" t="n"/>
       <c r="M23" s="83" t="n"/>
-      <c r="N23" s="81" t="n"/>
+      <c r="N23" s="81" t="n">
+        <v>94</v>
+      </c>
       <c r="O23" s="83" t="n"/>
       <c r="P23" s="83" t="n"/>
       <c r="Q23" s="83" t="n"/>
       <c r="R23" s="84" t="n"/>
       <c r="S23" s="85" t="n"/>
       <c r="T23" s="85" t="n"/>
-      <c r="U23" s="85" t="n"/>
+      <c r="U23" s="85" t="n">
+        <v>4</v>
+      </c>
       <c r="V23" s="85" t="n"/>
       <c r="W23" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="X23" s="86" t="n"/>
+      <c r="X23" s="86" t="n">
+        <v>95</v>
+      </c>
       <c r="Y23" s="87" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -3111,7 +3153,9 @@
           <t>Off balance sheet exposures subject to credit risk</t>
         </is>
       </c>
-      <c r="D24" s="91" t="n"/>
+      <c r="D24" s="91" t="n">
+        <v>94</v>
+      </c>
       <c r="E24" s="92" t="n"/>
       <c r="F24" s="67" t="n"/>
       <c r="G24" s="67" t="n"/>
@@ -3121,19 +3165,25 @@
       <c r="K24" s="93" t="n"/>
       <c r="L24" s="93" t="n"/>
       <c r="M24" s="93" t="n"/>
-      <c r="N24" s="93" t="n"/>
+      <c r="N24" s="93" t="n">
+        <v>95</v>
+      </c>
       <c r="O24" s="93" t="n"/>
       <c r="P24" s="93" t="n"/>
       <c r="Q24" s="93" t="n"/>
       <c r="R24" s="94" t="n"/>
       <c r="S24" s="94" t="n"/>
       <c r="T24" s="94" t="n"/>
-      <c r="U24" s="94" t="n"/>
+      <c r="U24" s="94" t="n">
+        <v>5</v>
+      </c>
       <c r="V24" s="94" t="n"/>
       <c r="W24" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="X24" s="95" t="n"/>
+      <c r="X24" s="95" t="n">
+        <v>96</v>
+      </c>
       <c r="Y24" s="96" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -3159,7 +3209,9 @@
           <t xml:space="preserve">Securities Financing Transactions </t>
         </is>
       </c>
-      <c r="D25" s="56" t="n"/>
+      <c r="D25" s="56" t="n">
+        <v>95</v>
+      </c>
       <c r="E25" s="98" t="n"/>
       <c r="F25" s="58" t="n"/>
       <c r="G25" s="58" t="n"/>
@@ -3169,19 +3221,25 @@
       <c r="K25" s="92" t="n"/>
       <c r="L25" s="92" t="n"/>
       <c r="M25" s="92" t="n"/>
-      <c r="N25" s="101" t="n"/>
+      <c r="N25" s="101" t="n">
+        <v>96</v>
+      </c>
       <c r="O25" s="93" t="n"/>
       <c r="P25" s="93" t="n"/>
       <c r="Q25" s="93" t="n"/>
       <c r="R25" s="59" t="n"/>
       <c r="S25" s="102" t="n"/>
       <c r="T25" s="102" t="n"/>
-      <c r="U25" s="102" t="n"/>
+      <c r="U25" s="102" t="n">
+        <v>6</v>
+      </c>
       <c r="V25" s="102" t="n"/>
       <c r="W25" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="X25" s="59" t="n"/>
+      <c r="X25" s="59" t="n">
+        <v>97</v>
+      </c>
       <c r="Y25" s="68" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -3207,7 +3265,9 @@
           <t>of which: centrally cleared through a QCCP</t>
         </is>
       </c>
-      <c r="D26" s="56" t="n"/>
+      <c r="D26" s="56" t="n">
+        <v>87</v>
+      </c>
       <c r="E26" s="98" t="n"/>
       <c r="F26" s="58" t="n"/>
       <c r="G26" s="105" t="n"/>
@@ -3217,19 +3277,25 @@
       <c r="K26" s="102" t="n"/>
       <c r="L26" s="102" t="n"/>
       <c r="M26" s="102" t="n"/>
-      <c r="N26" s="106" t="n"/>
+      <c r="N26" s="106" t="n">
+        <v>88</v>
+      </c>
       <c r="O26" s="102" t="n"/>
       <c r="P26" s="102" t="n"/>
       <c r="Q26" s="102" t="n"/>
       <c r="R26" s="98" t="n"/>
       <c r="S26" s="102" t="n"/>
       <c r="T26" s="102" t="n"/>
-      <c r="U26" s="102" t="n"/>
+      <c r="U26" s="102" t="n">
+        <v>95</v>
+      </c>
       <c r="V26" s="102" t="n"/>
       <c r="W26" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="X26" s="98" t="n"/>
+      <c r="X26" s="98" t="n">
+        <v>89</v>
+      </c>
       <c r="Y26" s="98" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -3255,7 +3321,9 @@
           <t>Derivatives &amp; Long Settlement Transactions</t>
         </is>
       </c>
-      <c r="D27" s="56" t="n"/>
+      <c r="D27" s="56" t="n">
+        <v>88</v>
+      </c>
       <c r="E27" s="98" t="n"/>
       <c r="F27" s="58" t="n"/>
       <c r="G27" s="58" t="n"/>
@@ -3265,19 +3333,25 @@
       <c r="K27" s="92" t="n"/>
       <c r="L27" s="92" t="n"/>
       <c r="M27" s="92" t="n"/>
-      <c r="N27" s="101" t="n"/>
+      <c r="N27" s="101" t="n">
+        <v>89</v>
+      </c>
       <c r="O27" s="92" t="n"/>
       <c r="P27" s="92" t="n"/>
       <c r="Q27" s="92" t="n"/>
       <c r="R27" s="59" t="n"/>
       <c r="S27" s="102" t="n"/>
       <c r="T27" s="102" t="n"/>
-      <c r="U27" s="102" t="n"/>
+      <c r="U27" s="102" t="n">
+        <v>96</v>
+      </c>
       <c r="V27" s="102" t="n"/>
       <c r="W27" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="X27" s="59" t="n"/>
+      <c r="X27" s="59" t="n">
+        <v>90</v>
+      </c>
       <c r="Y27" s="68" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -3303,7 +3377,9 @@
           <t>of which: centrally cleared through a QCCP</t>
         </is>
       </c>
-      <c r="D28" s="56" t="n"/>
+      <c r="D28" s="56" t="n">
+        <v>89</v>
+      </c>
       <c r="E28" s="98" t="n"/>
       <c r="F28" s="58" t="n"/>
       <c r="G28" s="105" t="n"/>
@@ -3313,19 +3389,25 @@
       <c r="K28" s="102" t="n"/>
       <c r="L28" s="102" t="n"/>
       <c r="M28" s="102" t="n"/>
-      <c r="N28" s="106" t="n"/>
+      <c r="N28" s="106" t="n">
+        <v>90</v>
+      </c>
       <c r="O28" s="102" t="n"/>
       <c r="P28" s="102" t="n"/>
       <c r="Q28" s="102" t="n"/>
       <c r="R28" s="98" t="n"/>
       <c r="S28" s="102" t="n"/>
       <c r="T28" s="102" t="n"/>
-      <c r="U28" s="102" t="n"/>
+      <c r="U28" s="102" t="n">
+        <v>97</v>
+      </c>
       <c r="V28" s="102" t="n"/>
       <c r="W28" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="X28" s="98" t="n"/>
+      <c r="X28" s="98" t="n">
+        <v>91</v>
+      </c>
       <c r="Y28" s="98" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -3351,7 +3433,9 @@
           <t>From Contractual Cross Product Netting</t>
         </is>
       </c>
-      <c r="D29" s="108" t="n"/>
+      <c r="D29" s="108" t="n">
+        <v>90</v>
+      </c>
       <c r="E29" s="109" t="n"/>
       <c r="F29" s="73" t="n"/>
       <c r="G29" s="73" t="n"/>
@@ -3361,19 +3445,25 @@
       <c r="K29" s="110" t="n"/>
       <c r="L29" s="110" t="n"/>
       <c r="M29" s="110" t="n"/>
-      <c r="N29" s="111" t="n"/>
+      <c r="N29" s="111" t="n">
+        <v>91</v>
+      </c>
       <c r="O29" s="110" t="n"/>
       <c r="P29" s="110" t="n"/>
       <c r="Q29" s="110" t="n"/>
       <c r="R29" s="74" t="n"/>
       <c r="S29" s="112" t="n"/>
       <c r="T29" s="112" t="n"/>
-      <c r="U29" s="112" t="n"/>
+      <c r="U29" s="112" t="n">
+        <v>1</v>
+      </c>
       <c r="V29" s="112" t="n"/>
       <c r="W29" s="74" t="n">
         <v>1</v>
       </c>
-      <c r="X29" s="74" t="n"/>
+      <c r="X29" s="74" t="n">
+        <v>92</v>
+      </c>
       <c r="Y29" s="113" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -3909,7 +3999,9 @@
           <t>Other risk weights</t>
         </is>
       </c>
-      <c r="D45" s="145" t="n"/>
+      <c r="D45" s="145" t="n">
+        <v>96</v>
+      </c>
       <c r="E45" s="146" t="n"/>
       <c r="F45" s="147" t="n"/>
       <c r="G45" s="147" t="n"/>
@@ -3919,19 +4011,25 @@
       <c r="K45" s="148" t="n"/>
       <c r="L45" s="148" t="n"/>
       <c r="M45" s="148" t="n"/>
-      <c r="N45" s="148" t="n"/>
+      <c r="N45" s="148" t="n">
+        <v>97</v>
+      </c>
       <c r="O45" s="148" t="n"/>
       <c r="P45" s="148" t="n"/>
       <c r="Q45" s="148" t="n"/>
       <c r="R45" s="149" t="n"/>
       <c r="S45" s="149" t="n"/>
       <c r="T45" s="149" t="n"/>
-      <c r="U45" s="149" t="n"/>
+      <c r="U45" s="149" t="n">
+        <v>7</v>
+      </c>
       <c r="V45" s="149" t="n"/>
       <c r="W45" s="149" t="n">
         <v>1</v>
       </c>
-      <c r="X45" s="149" t="n"/>
+      <c r="X45" s="149" t="n">
+        <v>1</v>
+      </c>
       <c r="Y45" s="150" t="inlineStr">
         <is>
           <t>TEST_OK</t>
@@ -4190,7 +4288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AB51"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="14"/>
   <cols>
     <col width="2.1640625" customWidth="1" style="1" min="1" max="1"/>
@@ -4856,20 +4954,28 @@
       <c r="K16" s="48" t="n"/>
       <c r="L16" s="48" t="n"/>
       <c r="M16" s="48" t="n"/>
-      <c r="N16" s="48" t="n"/>
+      <c r="N16" s="48" t="n">
+        <v>2</v>
+      </c>
       <c r="O16" s="47" t="n"/>
       <c r="P16" s="48" t="n"/>
       <c r="Q16" s="47" t="n"/>
       <c r="R16" s="49" t="n"/>
       <c r="S16" s="49" t="n"/>
       <c r="T16" s="49" t="n"/>
-      <c r="U16" s="49" t="n"/>
+      <c r="U16" s="49" t="n">
+        <v>9</v>
+      </c>
       <c r="V16" s="49" t="n"/>
-      <c r="W16" s="50" t="n"/>
+      <c r="W16" s="50" t="n">
+        <v>2</v>
+      </c>
       <c r="X16" s="51" t="n">
         <v>60</v>
       </c>
-      <c r="Y16" s="52" t="n"/>
+      <c r="Y16" s="52" t="n">
+        <v>8</v>
+      </c>
       <c r="Z16" s="51" t="inlineStr">
         <is>
           <t>Cell linked to CA</t>
@@ -4904,19 +5010,31 @@
       <c r="K17" s="58" t="n"/>
       <c r="L17" s="58" t="n"/>
       <c r="M17" s="58" t="n"/>
-      <c r="N17" s="58" t="n"/>
+      <c r="N17" s="58" t="n">
+        <v>3</v>
+      </c>
       <c r="O17" s="58" t="n"/>
       <c r="P17" s="58" t="n"/>
       <c r="Q17" s="58" t="n"/>
       <c r="R17" s="59" t="n"/>
       <c r="S17" s="59" t="n"/>
       <c r="T17" s="59" t="n"/>
-      <c r="U17" s="59" t="n"/>
+      <c r="U17" s="59" t="n">
+        <v>10</v>
+      </c>
       <c r="V17" s="59" t="n"/>
-      <c r="W17" s="60" t="n"/>
-      <c r="X17" s="60" t="n"/>
-      <c r="Y17" s="61" t="n"/>
-      <c r="Z17" s="60" t="n"/>
+      <c r="W17" s="60" t="n">
+        <v>3</v>
+      </c>
+      <c r="X17" s="60" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="61" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z17" s="60" t="n">
+        <v>5</v>
+      </c>
       <c r="AA17" s="62" t="n"/>
       <c r="AB17" s="63" t="n"/>
     </row>
@@ -4932,7 +5050,9 @@
           <t xml:space="preserve">of which: SME subject to SME-supporting factor </t>
         </is>
       </c>
-      <c r="D18" s="66" t="n"/>
+      <c r="D18" s="66" t="n">
+        <v>3</v>
+      </c>
       <c r="E18" s="57" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="67" t="n"/>
@@ -4942,19 +5062,31 @@
       <c r="K18" s="67" t="n"/>
       <c r="L18" s="67" t="n"/>
       <c r="M18" s="67" t="n"/>
-      <c r="N18" s="67" t="n"/>
+      <c r="N18" s="67" t="n">
+        <v>4</v>
+      </c>
       <c r="O18" s="67" t="n"/>
       <c r="P18" s="67" t="n"/>
       <c r="Q18" s="67" t="n"/>
       <c r="R18" s="68" t="n"/>
       <c r="S18" s="68" t="n"/>
       <c r="T18" s="68" t="n"/>
-      <c r="U18" s="68" t="n"/>
+      <c r="U18" s="68" t="n">
+        <v>11</v>
+      </c>
       <c r="V18" s="68" t="n"/>
-      <c r="W18" s="61" t="n"/>
-      <c r="X18" s="61" t="n"/>
-      <c r="Y18" s="61" t="n"/>
-      <c r="Z18" s="61" t="n"/>
+      <c r="W18" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="X18" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z18" s="61" t="n">
+        <v>6</v>
+      </c>
       <c r="AA18" s="62" t="n"/>
       <c r="AB18" s="63" t="n"/>
     </row>
@@ -5008,7 +5140,9 @@
           <t>of which: Exposures under the permanent partial use of the standardised approach</t>
         </is>
       </c>
-      <c r="D20" s="70" t="n"/>
+      <c r="D20" s="70" t="n">
+        <v>5</v>
+      </c>
       <c r="E20" s="57" t="n"/>
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="58" t="n"/>
@@ -5018,19 +5152,31 @@
       <c r="K20" s="58" t="n"/>
       <c r="L20" s="58" t="n"/>
       <c r="M20" s="58" t="n"/>
-      <c r="N20" s="58" t="n"/>
+      <c r="N20" s="58" t="n">
+        <v>6</v>
+      </c>
       <c r="O20" s="58" t="n"/>
       <c r="P20" s="58" t="n"/>
       <c r="Q20" s="58" t="n"/>
       <c r="R20" s="59" t="n"/>
       <c r="S20" s="59" t="n"/>
       <c r="T20" s="59" t="n"/>
-      <c r="U20" s="59" t="n"/>
+      <c r="U20" s="59" t="n">
+        <v>13</v>
+      </c>
       <c r="V20" s="59" t="n"/>
-      <c r="W20" s="60" t="n"/>
-      <c r="X20" s="60" t="n"/>
-      <c r="Y20" s="61" t="n"/>
-      <c r="Z20" s="60" t="n"/>
+      <c r="W20" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="X20" s="60" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y20" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z20" s="60" t="n">
+        <v>8</v>
+      </c>
       <c r="AA20" s="62" t="n"/>
       <c r="AB20" s="63" t="n"/>
     </row>
@@ -5046,7 +5192,9 @@
           <t>of which: Exposures under the standardised approach with prior supervisory permission to carry out a sequential IRB implementation</t>
         </is>
       </c>
-      <c r="D21" s="71" t="n"/>
+      <c r="D21" s="71" t="n">
+        <v>6</v>
+      </c>
       <c r="E21" s="72" t="n"/>
       <c r="F21" s="73" t="n"/>
       <c r="G21" s="73" t="n"/>
@@ -5056,19 +5204,31 @@
       <c r="K21" s="73" t="n"/>
       <c r="L21" s="73" t="n"/>
       <c r="M21" s="73" t="n"/>
-      <c r="N21" s="73" t="n"/>
+      <c r="N21" s="73" t="n">
+        <v>7</v>
+      </c>
       <c r="O21" s="73" t="n"/>
       <c r="P21" s="73" t="n"/>
       <c r="Q21" s="73" t="n"/>
       <c r="R21" s="74" t="n"/>
       <c r="S21" s="74" t="n"/>
       <c r="T21" s="74" t="n"/>
-      <c r="U21" s="74" t="n"/>
+      <c r="U21" s="74" t="n">
+        <v>14</v>
+      </c>
       <c r="V21" s="74" t="n"/>
-      <c r="W21" s="75" t="n"/>
-      <c r="X21" s="75" t="n"/>
-      <c r="Y21" s="76" t="n"/>
-      <c r="Z21" s="75" t="n"/>
+      <c r="W21" s="75" t="n">
+        <v>7</v>
+      </c>
+      <c r="X21" s="75" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="76" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z21" s="75" t="n">
+        <v>9</v>
+      </c>
       <c r="AA21" s="77" t="n"/>
       <c r="AB21" s="78" t="n"/>
     </row>
@@ -5130,19 +5290,31 @@
       <c r="K23" s="83" t="n"/>
       <c r="L23" s="83" t="n"/>
       <c r="M23" s="83" t="n"/>
-      <c r="N23" s="81" t="n"/>
+      <c r="N23" s="81" t="n">
+        <v>8</v>
+      </c>
       <c r="O23" s="83" t="n"/>
       <c r="P23" s="83" t="n"/>
       <c r="Q23" s="83" t="n"/>
       <c r="R23" s="84" t="n"/>
       <c r="S23" s="85" t="n"/>
       <c r="T23" s="85" t="n"/>
-      <c r="U23" s="85" t="n"/>
+      <c r="U23" s="85" t="n">
+        <v>15</v>
+      </c>
       <c r="V23" s="85" t="n"/>
-      <c r="W23" s="84" t="n"/>
-      <c r="X23" s="86" t="n"/>
-      <c r="Y23" s="87" t="n"/>
-      <c r="Z23" s="88" t="n"/>
+      <c r="W23" s="84" t="n">
+        <v>8</v>
+      </c>
+      <c r="X23" s="86" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y23" s="87" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" s="88" t="n">
+        <v>10</v>
+      </c>
       <c r="AA23" s="89" t="n"/>
       <c r="AB23" s="90" t="n"/>
     </row>
@@ -5158,7 +5330,9 @@
           <t>Off balance sheet exposures subject to credit risk</t>
         </is>
       </c>
-      <c r="D24" s="91" t="n"/>
+      <c r="D24" s="91" t="n">
+        <v>8</v>
+      </c>
       <c r="E24" s="92" t="n"/>
       <c r="F24" s="67" t="n"/>
       <c r="G24" s="67" t="n"/>
@@ -5168,19 +5342,31 @@
       <c r="K24" s="93" t="n"/>
       <c r="L24" s="93" t="n"/>
       <c r="M24" s="93" t="n"/>
-      <c r="N24" s="93" t="n"/>
+      <c r="N24" s="93" t="n">
+        <v>9</v>
+      </c>
       <c r="O24" s="93" t="n"/>
       <c r="P24" s="93" t="n"/>
       <c r="Q24" s="93" t="n"/>
       <c r="R24" s="94" t="n"/>
       <c r="S24" s="94" t="n"/>
       <c r="T24" s="94" t="n"/>
-      <c r="U24" s="94" t="n"/>
+      <c r="U24" s="94" t="n">
+        <v>16</v>
+      </c>
       <c r="V24" s="94" t="n"/>
-      <c r="W24" s="59" t="n"/>
-      <c r="X24" s="95" t="n"/>
-      <c r="Y24" s="96" t="n"/>
-      <c r="Z24" s="97" t="n"/>
+      <c r="W24" s="59" t="n">
+        <v>9</v>
+      </c>
+      <c r="X24" s="95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y24" s="96" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z24" s="97" t="n">
+        <v>11</v>
+      </c>
       <c r="AA24" s="98" t="n"/>
       <c r="AB24" s="99" t="n"/>
     </row>
@@ -5196,7 +5382,9 @@
           <t xml:space="preserve">Securities Financing Transactions </t>
         </is>
       </c>
-      <c r="D25" s="56" t="n"/>
+      <c r="D25" s="56" t="n">
+        <v>9</v>
+      </c>
       <c r="E25" s="98" t="n"/>
       <c r="F25" s="58" t="n"/>
       <c r="G25" s="58" t="n"/>
@@ -5206,21 +5394,31 @@
       <c r="K25" s="92" t="n"/>
       <c r="L25" s="92" t="n"/>
       <c r="M25" s="92" t="n"/>
-      <c r="N25" s="101" t="n"/>
+      <c r="N25" s="101" t="n">
+        <v>10</v>
+      </c>
       <c r="O25" s="93" t="n"/>
       <c r="P25" s="93" t="n"/>
       <c r="Q25" s="93" t="n"/>
       <c r="R25" s="59" t="n"/>
       <c r="S25" s="102" t="n"/>
       <c r="T25" s="102" t="n"/>
-      <c r="U25" s="102" t="n"/>
+      <c r="U25" s="102" t="n">
+        <v>17</v>
+      </c>
       <c r="V25" s="102" t="n"/>
-      <c r="W25" s="59" t="n"/>
+      <c r="W25" s="59" t="n">
+        <v>10</v>
+      </c>
       <c r="X25" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="Y25" s="68" t="n"/>
-      <c r="Z25" s="59" t="n"/>
+      <c r="Y25" s="68" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z25" s="59" t="n">
+        <v>12</v>
+      </c>
       <c r="AA25" s="98" t="n"/>
       <c r="AB25" s="99" t="n"/>
     </row>
@@ -5236,7 +5434,9 @@
           <t>of which: centrally cleared through a QCCP</t>
         </is>
       </c>
-      <c r="D26" s="56" t="n"/>
+      <c r="D26" s="56" t="n">
+        <v>1</v>
+      </c>
       <c r="E26" s="98" t="n"/>
       <c r="F26" s="58" t="n"/>
       <c r="G26" s="105" t="n"/>
@@ -5246,19 +5446,31 @@
       <c r="K26" s="102" t="n"/>
       <c r="L26" s="102" t="n"/>
       <c r="M26" s="102" t="n"/>
-      <c r="N26" s="106" t="n"/>
+      <c r="N26" s="106" t="n">
+        <v>2</v>
+      </c>
       <c r="O26" s="102" t="n"/>
       <c r="P26" s="102" t="n"/>
       <c r="Q26" s="102" t="n"/>
       <c r="R26" s="98" t="n"/>
       <c r="S26" s="102" t="n"/>
       <c r="T26" s="102" t="n"/>
-      <c r="U26" s="102" t="n"/>
+      <c r="U26" s="102" t="n">
+        <v>9</v>
+      </c>
       <c r="V26" s="102" t="n"/>
-      <c r="W26" s="59" t="n"/>
-      <c r="X26" s="98" t="n"/>
-      <c r="Y26" s="98" t="n"/>
-      <c r="Z26" s="98" t="n"/>
+      <c r="W26" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="X26" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="98" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z26" s="98" t="n">
+        <v>4</v>
+      </c>
       <c r="AA26" s="98" t="n"/>
       <c r="AB26" s="99" t="n"/>
     </row>
@@ -5274,7 +5486,9 @@
           <t>Derivatives &amp; Long Settlement Transactions</t>
         </is>
       </c>
-      <c r="D27" s="56" t="n"/>
+      <c r="D27" s="56" t="n">
+        <v>2</v>
+      </c>
       <c r="E27" s="98" t="n"/>
       <c r="F27" s="58" t="n"/>
       <c r="G27" s="58" t="n"/>
@@ -5284,20 +5498,31 @@
       <c r="K27" s="92" t="n"/>
       <c r="L27" s="92" t="n"/>
       <c r="M27" s="92" t="n"/>
-      <c r="N27" s="101" t="n"/>
+      <c r="N27" s="101" t="n">
+        <v>3</v>
+      </c>
       <c r="O27" s="92" t="n"/>
       <c r="P27" s="92" t="n"/>
       <c r="Q27" s="92" t="n"/>
       <c r="R27" s="59" t="n"/>
       <c r="S27" s="102" t="n"/>
       <c r="T27" s="102" t="n"/>
-      <c r="U27" s="102" t="n"/>
+      <c r="U27" s="102" t="n">
+        <v>10</v>
+      </c>
       <c r="V27" s="102" t="n"/>
-      <c r="W27" s="59" t="n"/>
+      <c r="W27" s="59" t="n">
+        <v>3</v>
+      </c>
       <c r="X27" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="Y27" s="68" t="n"/>
+      <c r="Y27" s="68" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5</v>
+      </c>
       <c r="AA27" s="98" t="n"/>
       <c r="AB27" s="99" t="n"/>
     </row>
@@ -5313,7 +5538,9 @@
           <t>of which: centrally cleared through a QCCP</t>
         </is>
       </c>
-      <c r="D28" s="56" t="n"/>
+      <c r="D28" s="56" t="n">
+        <v>3</v>
+      </c>
       <c r="E28" s="98" t="n"/>
       <c r="F28" s="58" t="n"/>
       <c r="G28" s="105" t="n"/>
@@ -5323,19 +5550,31 @@
       <c r="K28" s="102" t="n"/>
       <c r="L28" s="102" t="n"/>
       <c r="M28" s="102" t="n"/>
-      <c r="N28" s="106" t="n"/>
+      <c r="N28" s="106" t="n">
+        <v>4</v>
+      </c>
       <c r="O28" s="102" t="n"/>
       <c r="P28" s="102" t="n"/>
       <c r="Q28" s="102" t="n"/>
       <c r="R28" s="98" t="n"/>
       <c r="S28" s="102" t="n"/>
       <c r="T28" s="102" t="n"/>
-      <c r="U28" s="102" t="n"/>
+      <c r="U28" s="102" t="n">
+        <v>11</v>
+      </c>
       <c r="V28" s="102" t="n"/>
-      <c r="W28" s="59" t="n"/>
-      <c r="X28" s="98" t="n"/>
-      <c r="Y28" s="98" t="n"/>
-      <c r="Z28" s="98" t="n"/>
+      <c r="W28" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="X28" s="98" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y28" s="98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" s="98" t="n">
+        <v>6</v>
+      </c>
       <c r="AA28" s="98" t="n"/>
       <c r="AB28" s="99" t="n"/>
     </row>
@@ -5351,7 +5590,9 @@
           <t>From Contractual Cross Product Netting</t>
         </is>
       </c>
-      <c r="D29" s="108" t="n"/>
+      <c r="D29" s="108" t="n">
+        <v>4</v>
+      </c>
       <c r="E29" s="109" t="n"/>
       <c r="F29" s="73" t="n"/>
       <c r="G29" s="73" t="n"/>
@@ -5361,20 +5602,31 @@
       <c r="K29" s="110" t="n"/>
       <c r="L29" s="110" t="n"/>
       <c r="M29" s="110" t="n"/>
-      <c r="N29" s="111" t="n"/>
+      <c r="N29" s="111" t="n">
+        <v>5</v>
+      </c>
       <c r="O29" s="110" t="n"/>
       <c r="P29" s="110" t="n"/>
       <c r="Q29" s="110" t="n"/>
       <c r="R29" s="74" t="n"/>
       <c r="S29" s="112" t="n"/>
       <c r="T29" s="112" t="n"/>
-      <c r="U29" s="112" t="n"/>
+      <c r="U29" s="112" t="n">
+        <v>12</v>
+      </c>
       <c r="V29" s="112" t="n"/>
-      <c r="W29" s="74" t="n"/>
+      <c r="W29" s="74" t="n">
+        <v>5</v>
+      </c>
       <c r="X29" s="74" t="n">
         <v>30</v>
       </c>
-      <c r="Y29" s="113" t="n"/>
+      <c r="Y29" s="113" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7</v>
+      </c>
       <c r="AA29" s="109" t="n"/>
       <c r="AB29" s="114" t="n"/>
     </row>
@@ -5902,7 +6154,9 @@
           <t>Other risk weights</t>
         </is>
       </c>
-      <c r="D45" s="145" t="n"/>
+      <c r="D45" s="145" t="n">
+        <v>10</v>
+      </c>
       <c r="E45" s="146" t="n"/>
       <c r="F45" s="147" t="n"/>
       <c r="G45" s="147" t="n"/>
@@ -5912,19 +6166,31 @@
       <c r="K45" s="148" t="n"/>
       <c r="L45" s="148" t="n"/>
       <c r="M45" s="148" t="n"/>
-      <c r="N45" s="148" t="n"/>
+      <c r="N45" s="148" t="n">
+        <v>11</v>
+      </c>
       <c r="O45" s="148" t="n"/>
       <c r="P45" s="148" t="n"/>
       <c r="Q45" s="148" t="n"/>
       <c r="R45" s="149" t="n"/>
       <c r="S45" s="149" t="n"/>
       <c r="T45" s="149" t="n"/>
-      <c r="U45" s="149" t="n"/>
+      <c r="U45" s="149" t="n">
+        <v>18</v>
+      </c>
       <c r="V45" s="149" t="n"/>
-      <c r="W45" s="149" t="n"/>
-      <c r="X45" s="149" t="n"/>
-      <c r="Y45" s="150" t="n"/>
-      <c r="Z45" s="149" t="n"/>
+      <c r="W45" s="149" t="n">
+        <v>11</v>
+      </c>
+      <c r="X45" s="149" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y45" s="150" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z45" s="149" t="n">
+        <v>13</v>
+      </c>
       <c r="AA45" s="149" t="n"/>
       <c r="AB45" s="151" t="n"/>
     </row>
